--- a/artfynd/A 39554-2023 artfynd.xlsx
+++ b/artfynd/A 39554-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122549327</v>
       </c>
       <c r="B2" t="n">
-        <v>78040</v>
+        <v>78041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 39554-2023 artfynd.xlsx
+++ b/artfynd/A 39554-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122549327</v>
       </c>
       <c r="B2" t="n">
-        <v>78041</v>
+        <v>78044</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 39554-2023 artfynd.xlsx
+++ b/artfynd/A 39554-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122549327</v>
       </c>
       <c r="B2" t="n">
-        <v>78044</v>
+        <v>78146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 39554-2023 artfynd.xlsx
+++ b/artfynd/A 39554-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122549327</v>
       </c>
       <c r="B2" t="n">
-        <v>78146</v>
+        <v>78150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
